--- a/宝宝辅食食材排敏与添加指南.xlsx
+++ b/宝宝辅食食材排敏与添加指南.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12940"/>
+    <workbookView windowWidth="29400" windowHeight="13060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="243">
   <si>
     <t>分类类型</t>
   </si>
@@ -74,145 +74,136 @@
     <t>辅食第一口，单独吃5天，优先补铁</t>
   </si>
   <si>
-    <t>小米泥</t>
-  </si>
-  <si>
-    <t>小米淘洗后浸泡30分钟，煮至软烂打泥</t>
+    <t>小米</t>
+  </si>
+  <si>
+    <t>小米淘洗后浸泡30分钟，煮至软烂打</t>
   </si>
   <si>
     <t>无添加纯小米，避免调味，易消化</t>
   </si>
   <si>
-    <t>燕麦泥</t>
+    <t>燕麦</t>
   </si>
   <si>
     <t>6月龄</t>
   </si>
   <si>
-    <t>纯燕麦片煮软打泥，无额外糖、奶添加</t>
+    <t>纯燕麦片煮软打，无额外糖、奶添加</t>
   </si>
   <si>
     <t>选无麸质敏感款，单独排敏3天</t>
   </si>
   <si>
-    <t>藜麦泥</t>
-  </si>
-  <si>
-    <t>藜麦浸泡2小时去皂苷，煮熟后打泥</t>
+    <t>藜麦</t>
+  </si>
+  <si>
+    <t>藜麦浸泡2小时去皂苷，煮熟后打</t>
   </si>
   <si>
     <t>优质蛋白谷物，首次1小勺起步</t>
   </si>
   <si>
-    <t>大米粥泥</t>
-  </si>
-  <si>
-    <t>大米淘洗煮烂，取粥底压成细泥</t>
+    <t>大米粥</t>
+  </si>
+  <si>
+    <t>大米淘洗煮烂，取粥底压成细</t>
   </si>
   <si>
     <t>基础谷物，适配肠胃适应期</t>
   </si>
   <si>
-    <t>糙米泥</t>
+    <t>糙米</t>
   </si>
   <si>
     <t>7月龄</t>
   </si>
   <si>
-    <t>糙米浸泡4小时，煮软打泥（可混合大米煮）</t>
+    <t>糙米浸泡4小时，煮软打（可混合大米煮）</t>
   </si>
   <si>
     <t>膳食纤维丰富，少量添加防胀气</t>
   </si>
   <si>
-    <t>玉米泥</t>
-  </si>
-  <si>
-    <t>甜玉米去皮去须，蒸熟取玉米粒打泥</t>
-  </si>
-  <si>
-    <t>选嫩玉米，打泥后过筛去残留纤维</t>
-  </si>
-  <si>
-    <t>高粱泥</t>
-  </si>
-  <si>
-    <t>高粱米浸泡4小时，煮软打泥</t>
-  </si>
-  <si>
-    <t>口感细腻，搭配其他谷物吃更均衡</t>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>甜玉米去皮去须，蒸熟取玉米粒打</t>
+  </si>
+  <si>
+    <t>选嫩玉米，打后过筛去残留纤维</t>
   </si>
   <si>
     <t>淀粉类根茎蔬菜</t>
   </si>
   <si>
-    <t>土豆泥</t>
-  </si>
-  <si>
-    <t>土豆去皮蒸熟，压成无颗粒细泥（手指可捻碎）</t>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>土豆去皮蒸熟，压成无颗粒细（手指可捻碎）</t>
   </si>
   <si>
     <t>低敏易吸收，首次1小勺，补充碳水</t>
   </si>
   <si>
-    <t>南瓜泥</t>
-  </si>
-  <si>
-    <t>南瓜去皮去籽蒸熟，打泥</t>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>南瓜去皮去籽蒸熟，打</t>
   </si>
   <si>
     <t>含糖量稍高，每日不超过2小勺，防胀气</t>
   </si>
   <si>
-    <t>山药泥</t>
-  </si>
-  <si>
-    <t>山药去皮蒸熟（戴手套防黏液刺激），打泥</t>
+    <t>山药</t>
+  </si>
+  <si>
+    <t>山药去皮蒸熟（戴手套防黏液刺激），打</t>
   </si>
   <si>
     <t>健脾养胃，彻底蒸熟避免生涩刺激</t>
   </si>
   <si>
-    <t>莲藕泥</t>
-  </si>
-  <si>
-    <t>莲藕去皮切小块，煮熟打泥，去藕节硬纤维</t>
+    <t>莲藕</t>
+  </si>
+  <si>
+    <t>莲藕去皮切小块，煮熟打，去藕节硬纤维</t>
   </si>
   <si>
     <t>清热易消化，煮至软烂无颗粒</t>
   </si>
   <si>
-    <t>红薯泥</t>
-  </si>
-  <si>
-    <t>红薯去皮蒸熟，压泥</t>
+    <t>红薯</t>
+  </si>
+  <si>
+    <t>红薯去皮蒸熟，压</t>
   </si>
   <si>
     <t>膳食纤维丰富，少量吃防便秘</t>
   </si>
   <si>
-    <t>紫薯泥</t>
-  </si>
-  <si>
-    <t>紫薯去皮蒸熟，打泥</t>
+    <t>紫薯</t>
+  </si>
+  <si>
+    <t>紫薯去皮蒸熟，打</t>
   </si>
   <si>
     <t>花青素丰富，颜色鲜艳易吸引宝宝</t>
   </si>
   <si>
-    <t>芋头泥</t>
-  </si>
-  <si>
-    <t>芋头去皮蒸熟，打泥（生芋头过敏者戴手套处理）</t>
+    <t>芋头</t>
+  </si>
+  <si>
+    <t>芋头去皮蒸熟，打（生芋头过敏者戴手套处理）</t>
   </si>
   <si>
     <t>口感绵密，首次少量，防轻微胀气</t>
   </si>
   <si>
-    <t>菱角泥</t>
-  </si>
-  <si>
-    <t>菱角去皮，煮熟煮透打泥</t>
+    <t>菱角</t>
+  </si>
+  <si>
+    <t>菱角去皮，煮熟煮透打</t>
   </si>
   <si>
     <t>需彻底煮熟，避免残留细菌</t>
@@ -221,85 +212,85 @@
     <t>绿叶蔬菜类</t>
   </si>
   <si>
-    <t>菠菜泥</t>
-  </si>
-  <si>
-    <t>菠菜洗净焯水1分钟去草酸，切碎煮熟打泥</t>
+    <t>菠菜</t>
+  </si>
+  <si>
+    <t>菠菜洗净焯水1分钟去草酸，切碎煮熟打</t>
   </si>
   <si>
     <t>不空腹添加，补充铁和维生素</t>
   </si>
   <si>
-    <t>西兰花泥</t>
-  </si>
-  <si>
-    <t>西兰花去粗茎切小朵，焯水后蒸熟打泥</t>
-  </si>
-  <si>
-    <t>打泥后过筛，去除不易消化的粗纤维</t>
-  </si>
-  <si>
-    <t>油麦菜泥</t>
-  </si>
-  <si>
-    <t>油麦菜洗净焯水，取嫩叶切碎打泥</t>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>西兰花去粗茎切小朵，焯水后蒸熟打</t>
+  </si>
+  <si>
+    <t>打后过筛，去除不易消化的粗纤维</t>
+  </si>
+  <si>
+    <t>油麦菜</t>
+  </si>
+  <si>
+    <t>油麦菜洗净焯水，取嫩叶切碎打</t>
   </si>
   <si>
     <t>水分充足，口感清淡适配初加蔬菜</t>
   </si>
   <si>
-    <t>生菜泥</t>
-  </si>
-  <si>
-    <t>生菜洗净焯水，打泥</t>
+    <t>生菜</t>
+  </si>
+  <si>
+    <t>生菜洗净焯水，打</t>
   </si>
   <si>
     <t>选奶油生菜，彻底清洗去农药残留</t>
   </si>
   <si>
-    <t>油菜泥</t>
-  </si>
-  <si>
-    <t>油菜洗净焯水，切碎打泥</t>
+    <t>油菜</t>
+  </si>
+  <si>
+    <t>油菜洗净焯水，切碎打</t>
   </si>
   <si>
     <t>低敏无刺激，日常可频繁添加</t>
   </si>
   <si>
-    <t>娃娃菜泥</t>
-  </si>
-  <si>
-    <t>娃娃菜洗净焯水，切碎打泥</t>
+    <t>娃娃菜</t>
+  </si>
+  <si>
+    <t>娃娃菜洗净焯水，切碎打</t>
   </si>
   <si>
     <t>口感软嫩，易被宝宝肠胃接受</t>
   </si>
   <si>
-    <t>芥蓝泥</t>
-  </si>
-  <si>
-    <t>芥蓝去老茎焯水，煮熟打泥</t>
+    <t>芥蓝</t>
+  </si>
+  <si>
+    <t>芥蓝去老茎焯水，煮熟打</t>
   </si>
   <si>
     <t>少量添加，避免口感偏苦影响接受度</t>
   </si>
   <si>
-    <t>茼蒿泥</t>
+    <t>茼蒿</t>
   </si>
   <si>
     <t>8月龄</t>
   </si>
   <si>
-    <t>茼蒿洗净焯水，切碎打泥</t>
+    <t>茼蒿洗净焯水，切碎打</t>
   </si>
   <si>
     <t>清热利湿，煮熟后苦味减轻</t>
   </si>
   <si>
-    <t>菠菜苗泥</t>
-  </si>
-  <si>
-    <t>菠菜苗洗净焯水，打泥</t>
+    <t>菠菜苗</t>
+  </si>
+  <si>
+    <t>菠菜苗洗净焯水，打</t>
   </si>
   <si>
     <t>草酸含量低于成熟菠菜，更易吸收</t>
@@ -308,64 +299,64 @@
     <t>瓜茄类蔬菜</t>
   </si>
   <si>
-    <t>黄瓜泥</t>
-  </si>
-  <si>
-    <t>黄瓜去皮去瓤，蒸熟打泥</t>
+    <t>黄瓜</t>
+  </si>
+  <si>
+    <t>黄瓜去皮去瓤，蒸熟打</t>
   </si>
   <si>
     <t>不生吃，避免生冷刺激肠胃</t>
   </si>
   <si>
-    <t>番茄泥</t>
-  </si>
-  <si>
-    <t>番茄烫皮去籽，蒸熟打泥</t>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>番茄烫皮去籽，蒸熟打</t>
   </si>
   <si>
     <t>减少酸性刺激，首次少量防反酸</t>
   </si>
   <si>
-    <t>西葫芦泥</t>
-  </si>
-  <si>
-    <t>西葫芦去皮切小块，煮熟打泥</t>
+    <t>西葫芦</t>
+  </si>
+  <si>
+    <t>西葫芦去皮切小块，煮熟打</t>
   </si>
   <si>
     <t>低敏低卡，日常辅食高频选择</t>
   </si>
   <si>
-    <t>冬瓜泥</t>
-  </si>
-  <si>
-    <t>冬瓜去皮去瓤，煮熟打泥</t>
+    <t>冬瓜</t>
+  </si>
+  <si>
+    <t>冬瓜去皮去瓤，煮熟打</t>
   </si>
   <si>
     <t>水分充足，清热利尿</t>
   </si>
   <si>
-    <t>丝瓜泥</t>
-  </si>
-  <si>
-    <t>丝瓜去皮去瓤，煮熟打泥</t>
+    <t>丝瓜</t>
+  </si>
+  <si>
+    <t>丝瓜去皮去瓤，煮熟打</t>
   </si>
   <si>
     <t>口感软嫩，夏季辅食优选</t>
   </si>
   <si>
-    <t>苦瓜泥</t>
-  </si>
-  <si>
-    <t>苦瓜去籽去瓤，焯水后煮熟打泥</t>
+    <t>苦瓜</t>
+  </si>
+  <si>
+    <t>苦瓜去籽去瓤，焯水后煮熟打</t>
   </si>
   <si>
     <t>苦味重，每次仅1小勺，清热降火</t>
   </si>
   <si>
-    <t>彩椒泥（甜椒）</t>
-  </si>
-  <si>
-    <t>彩椒去皮去籽，煮熟打泥</t>
+    <t>彩椒（甜椒）</t>
+  </si>
+  <si>
+    <t>彩椒去皮去籽，煮熟打</t>
   </si>
   <si>
     <t>选甜椒无辣味，补充维生素C</t>
@@ -374,70 +365,70 @@
     <t>低糖低酸水果类</t>
   </si>
   <si>
-    <t>苹果泥</t>
-  </si>
-  <si>
-    <t>苹果去皮去核，蒸熟5-10分钟打泥</t>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>苹果去皮去核，蒸熟5-10分钟打</t>
   </si>
   <si>
     <t>蒸软后降低生冷刺激，适配肠胃初期</t>
   </si>
   <si>
-    <t>梨泥</t>
-  </si>
-  <si>
-    <t>梨去皮去核，蒸熟打泥</t>
+    <t>梨</t>
+  </si>
+  <si>
+    <t>梨去皮去核，蒸熟打</t>
   </si>
   <si>
     <t>缓解轻微便秘，餐后少量吃</t>
   </si>
   <si>
-    <t>香蕉泥</t>
-  </si>
-  <si>
-    <t>选熟软无黑斑香蕉，直接压成细泥</t>
+    <t>香蕉</t>
+  </si>
+  <si>
+    <t>选熟软无黑斑香蕉，直接压成细</t>
   </si>
   <si>
     <t>每日≤1/4根，避免糖分过高致腹胀</t>
   </si>
   <si>
-    <t>木瓜泥</t>
-  </si>
-  <si>
-    <t>木瓜去皮去籽，取果肉蒸熟打泥</t>
+    <t>木瓜</t>
+  </si>
+  <si>
+    <t>木瓜去皮去籽，取果肉蒸熟打</t>
   </si>
   <si>
     <t>含木瓜蛋白酶，助力消化</t>
   </si>
   <si>
-    <t>白心火龙果泥</t>
-  </si>
-  <si>
-    <t>火龙果去皮，取果肉压泥</t>
+    <t>白心火龙果</t>
+  </si>
+  <si>
+    <t>火龙果去皮，取果肉压</t>
   </si>
   <si>
     <t>膳食纤维丰富，少量吃防腹泻</t>
   </si>
   <si>
-    <t>猕猴桃泥</t>
-  </si>
-  <si>
-    <t>猕猴桃去皮，取果肉压泥（1岁内少量）</t>
+    <t>猕猴桃</t>
+  </si>
+  <si>
+    <t>猕猴桃去皮，取果肉压（1岁内少量）</t>
   </si>
   <si>
     <t>补充维生素C，首次1小勺起步</t>
   </si>
   <si>
-    <t>草莓泥</t>
-  </si>
-  <si>
-    <t>草莓洗净去蒂，焯水10秒后压泥</t>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>草莓洗净去蒂，焯水10秒后压</t>
   </si>
   <si>
     <t>易残留农药，彻底清洗，少量添加</t>
   </si>
   <si>
-    <t>蓝莓泥</t>
+    <t>蓝莓</t>
   </si>
   <si>
     <t>蓝莓洗净，蒸熟后压碎（去果蒂）</t>
@@ -446,10 +437,10 @@
     <t>花青素丰富，压碎后防呛咳</t>
   </si>
   <si>
-    <t>桃子泥（软桃）</t>
-  </si>
-  <si>
-    <t>桃子去皮去核，蒸熟打泥</t>
+    <t>桃子（软桃）</t>
+  </si>
+  <si>
+    <t>桃子去皮去核，蒸熟打</t>
   </si>
   <si>
     <t>选软桃无硬纤维，避免果皮接触皮肤</t>
@@ -458,64 +449,64 @@
     <t>菌菇类</t>
   </si>
   <si>
-    <t>香菇泥</t>
-  </si>
-  <si>
-    <t>香菇去蒂洗净，蒸熟打泥</t>
+    <t>香菇</t>
+  </si>
+  <si>
+    <t>香菇去蒂洗净，蒸熟打</t>
   </si>
   <si>
     <t>彻底煮熟，避免细菌残留，补多糖</t>
   </si>
   <si>
-    <t>平菇泥</t>
-  </si>
-  <si>
-    <t>平菇洗净撕碎，煮熟打泥</t>
+    <t>平菇</t>
+  </si>
+  <si>
+    <t>平菇洗净撕碎，煮熟打</t>
   </si>
   <si>
     <t>无异味无霉变，新鲜食材优先</t>
   </si>
   <si>
-    <t>金针菇泥</t>
-  </si>
-  <si>
-    <t>金针菇去根部，煮软后剪碎打泥</t>
+    <t>金针菇</t>
+  </si>
+  <si>
+    <t>金针菇去根部，煮软后剪碎打</t>
   </si>
   <si>
     <t>去除硬纤维，防止呛咳</t>
   </si>
   <si>
-    <t>杏鲍菇泥</t>
-  </si>
-  <si>
-    <t>杏鲍菇去皮切小块，煮熟打泥</t>
+    <t>杏鲍菇</t>
+  </si>
+  <si>
+    <t>杏鲍菇去皮切小块，煮熟打</t>
   </si>
   <si>
     <t>口感绵密，易被宝宝接受</t>
   </si>
   <si>
-    <t>蟹味菇泥</t>
-  </si>
-  <si>
-    <t>蟹味菇去根部洗净，煮熟打泥</t>
+    <t>蟹味菇</t>
+  </si>
+  <si>
+    <t>蟹味菇去根部洗净，煮熟打</t>
   </si>
   <si>
     <t>味道清淡，营养均衡</t>
   </si>
   <si>
-    <t>白玉菇泥</t>
-  </si>
-  <si>
-    <t>白玉菇去根部洗净，煮熟打泥</t>
+    <t>白玉菇</t>
+  </si>
+  <si>
+    <t>白玉菇去根部洗净，煮熟打</t>
   </si>
   <si>
     <t>彻底煮熟，避免残留杂质</t>
   </si>
   <si>
-    <t>口蘑泥</t>
-  </si>
-  <si>
-    <t>口蘑洗净切小块，蒸熟打泥</t>
+    <t>口蘑</t>
+  </si>
+  <si>
+    <t>口蘑洗净切小块，蒸熟打</t>
   </si>
   <si>
     <t>肉质细嫩，无额外异味</t>
@@ -533,130 +524,106 @@
     <t>中敏</t>
   </si>
   <si>
-    <t>取1/8个蛋黄，蒸成蛋羹或压泥</t>
+    <t>取1/8个蛋黄，蒸成蛋羹或压</t>
   </si>
   <si>
     <t>观察5天，无异常逐步增至1/4、1/2个</t>
   </si>
   <si>
-    <t>猪肉泥</t>
-  </si>
-  <si>
-    <t>选猪里脊瘦肉，去筋膜蒸熟打泥</t>
+    <t>猪肉</t>
+  </si>
+  <si>
+    <t>选猪里脊瘦肉，去筋膜蒸熟打</t>
   </si>
   <si>
     <t>避免肥肉，减少肠胃负担，补蛋白质</t>
   </si>
   <si>
-    <t>鸡肉泥</t>
-  </si>
-  <si>
-    <t>鸡胸肉去皮去骨，蒸熟打泥</t>
+    <t>鸡肉</t>
+  </si>
+  <si>
+    <t>鸡胸肉去皮去骨，蒸熟打</t>
   </si>
   <si>
     <t>低脂高蛋白，单独排敏5天</t>
   </si>
   <si>
-    <t>牛肉泥</t>
-  </si>
-  <si>
-    <t>选牛里脊，剔除筋膜蒸熟打泥（无颗粒）</t>
+    <t>牛肉</t>
+  </si>
+  <si>
+    <t>选牛里脊，剔除筋膜蒸熟打（无颗粒）</t>
   </si>
   <si>
     <t>红肉补铁，首次1小勺，观察消化情况</t>
   </si>
   <si>
-    <t>羊肉泥</t>
-  </si>
-  <si>
-    <t>选瘦羊肉去筋膜，蒸熟打泥（可加1片生姜去膻，蒸熟后取出）</t>
+    <t>羊肉</t>
+  </si>
+  <si>
+    <t>选瘦羊肉去筋膜，蒸熟打（可加1片生姜去膻，蒸熟后取出）</t>
   </si>
   <si>
     <t>少量起步，观察是否上火或过敏</t>
   </si>
   <si>
-    <t>鸭肉泥</t>
-  </si>
-  <si>
-    <t>鸭胸肉去皮去筋膜，蒸熟打泥</t>
+    <t>鸭肉</t>
+  </si>
+  <si>
+    <t>鸭胸肉去皮去筋膜，蒸熟打</t>
   </si>
   <si>
     <t>温润低脂，适合肠胃敏感宝宝</t>
   </si>
   <si>
-    <t>三文鱼泥</t>
+    <t>三文鱼</t>
   </si>
   <si>
     <t>9月龄</t>
   </si>
   <si>
-    <t>三文鱼去皮去刺，蒸熟打泥</t>
+    <t>三文鱼去皮去刺，蒸熟打</t>
   </si>
   <si>
     <t>低汞鱼补DHA，每周≤2次</t>
   </si>
   <si>
-    <t>鳕鱼泥</t>
-  </si>
-  <si>
-    <t>鳕鱼去皮去骨，蒸熟打泥</t>
+    <t>鳕鱼</t>
+  </si>
+  <si>
+    <t>鳕鱼去皮去骨，蒸熟打</t>
   </si>
   <si>
     <t>肉质细嫩易消化，单独排敏5天</t>
   </si>
   <si>
-    <t>鲈鱼泥</t>
-  </si>
-  <si>
-    <t>鲈鱼去皮去刺，蒸熟打泥（去净细刺）</t>
+    <t>鲈鱼</t>
+  </si>
+  <si>
+    <t>鲈鱼去皮去刺，蒸熟打（去净细刺）</t>
   </si>
   <si>
     <t>淡水低汞鱼，营养均衡，每周1-2次</t>
   </si>
   <si>
-    <t>猪肝泥</t>
+    <t>猪肝</t>
   </si>
   <si>
     <t>10月龄</t>
   </si>
   <si>
-    <t>猪肝洗净去血沫，蒸熟后打泥（过筛去颗粒）</t>
+    <t>猪肝洗净去血沫，蒸熟后打（过筛去颗粒）</t>
   </si>
   <si>
     <t>补铁佳品，每周≤1次，每次≤5g</t>
   </si>
   <si>
-    <t>鸡肝泥</t>
-  </si>
-  <si>
-    <t>鸡肝洗净去筋膜，蒸熟打泥（过筛）</t>
-  </si>
-  <si>
-    <t>铁含量丰富，口感比猪肝细腻</t>
-  </si>
-  <si>
-    <t>鸭肝泥</t>
-  </si>
-  <si>
-    <t>鸭肝洗净去血沫，蒸熟打泥（过筛）</t>
-  </si>
-  <si>
-    <t>每周1次，搭配蔬菜吃更易吸收</t>
-  </si>
-  <si>
-    <t>三文鱼松（细腻款）</t>
-  </si>
-  <si>
-    <t>三文鱼蒸熟打泥后小火炒干，研磨成松</t>
+    <t>三文鱼蒸熟打后小火炒干，研磨成松</t>
   </si>
   <si>
     <t>无盐无添加，少量撒入粥/米粉</t>
   </si>
   <si>
-    <t>鳕鱼松</t>
-  </si>
-  <si>
-    <t>鳕鱼蒸熟打泥炒干，研磨成松</t>
+    <t>鳕鱼蒸熟打炒干，研磨成松</t>
   </si>
   <si>
     <t>口感清淡，适配宝宝味觉</t>
@@ -707,85 +674,85 @@
     <t>过敏风险高，严格观察7天</t>
   </si>
   <si>
-    <t>黄豆泥</t>
-  </si>
-  <si>
-    <t>黄豆提前浸泡4小时，煮熟煮透打泥</t>
+    <t>黄豆</t>
+  </si>
+  <si>
+    <t>黄豆提前浸泡4小时，煮熟煮透打</t>
   </si>
   <si>
     <t>观察胀气，不空腹添加，观察7天</t>
   </si>
   <si>
-    <t>黑豆泥</t>
-  </si>
-  <si>
-    <t>黑豆提前浸泡6小时，煮熟煮透打泥</t>
+    <t>黑豆</t>
+  </si>
+  <si>
+    <t>黑豆提前浸泡6小时，煮熟煮透打</t>
   </si>
   <si>
     <t>营养丰富，少量添加防肠胃不适</t>
   </si>
   <si>
-    <t>扁豆泥</t>
-  </si>
-  <si>
-    <t>扁豆提前浸泡4小时，煮熟煮透打泥</t>
+    <t>扁豆</t>
+  </si>
+  <si>
+    <t>扁豆提前浸泡4小时，煮熟煮透打</t>
   </si>
   <si>
     <t>彻底煮熟，避免有毒物质残留</t>
   </si>
   <si>
-    <t>芒果泥</t>
+    <t>芒果</t>
   </si>
   <si>
     <t>1岁+</t>
   </si>
   <si>
-    <t>芒果去皮去籽，取少量果肉打泥</t>
+    <t>芒果去皮去籽，取少量果肉打</t>
   </si>
   <si>
     <t>避开果皮/果汁防接触性过敏，观察7天</t>
   </si>
   <si>
-    <t>菠萝泥</t>
-  </si>
-  <si>
-    <t>菠萝果肉盐水浸泡10分钟，冲洗后打泥</t>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>菠萝果肉盐水浸泡10分钟，冲洗后打</t>
   </si>
   <si>
     <t>去菠萝蛋白酶，减少刺激，观察7天</t>
   </si>
   <si>
-    <t>绿心猕猴桃泥</t>
-  </si>
-  <si>
-    <t>绿心猕猴桃去皮，取少量果肉压泥</t>
+    <t>绿心猕猴桃</t>
+  </si>
+  <si>
+    <t>绿心猕猴桃去皮，取少量果肉压</t>
   </si>
   <si>
     <t>酸性较强，首次极少量，观察过敏</t>
   </si>
   <si>
-    <t>荔枝泥</t>
-  </si>
-  <si>
-    <t>荔枝去皮去核，取少量果肉压泥</t>
+    <t>荔枝</t>
+  </si>
+  <si>
+    <t>荔枝去皮去核，取少量果肉压</t>
   </si>
   <si>
     <t>含糖量高易上火，每次1-2瓣</t>
   </si>
   <si>
-    <t>龙眼泥</t>
-  </si>
-  <si>
-    <t>龙眼去皮去核，取少量果肉压泥</t>
+    <t>龙眼</t>
+  </si>
+  <si>
+    <t>龙眼去皮去核，取少量果肉压</t>
   </si>
   <si>
     <t>温热性水果，少量添加防上火</t>
   </si>
   <si>
-    <t>虾仁泥</t>
-  </si>
-  <si>
-    <t>虾仁去虾线洗净，蒸熟打泥</t>
+    <t>虾仁</t>
+  </si>
+  <si>
+    <t>虾仁去虾线洗净，蒸熟打</t>
   </si>
   <si>
     <t>海鲜过敏风险高，观察7天，每周≤1次</t>
@@ -801,7 +768,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -812,13 +779,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1286,148 +1246,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1782,7 +1742,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="6" width="17.625" customWidth="1"/>
@@ -2003,25 +1963,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2029,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>39</v>
@@ -2055,16 +2015,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -2081,7 +2041,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
@@ -2090,7 +2050,7 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2107,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>48</v>
@@ -2116,7 +2076,7 @@
         <v>19</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -2133,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -2159,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>54</v>
@@ -2168,7 +2128,7 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -2185,7 +2145,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>57</v>
@@ -2194,7 +2154,7 @@
         <v>29</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -2211,25 +2171,25 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2237,7 +2197,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
         <v>64</v>
@@ -2246,7 +2206,7 @@
         <v>19</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -2263,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
         <v>67</v>
@@ -2272,7 +2232,7 @@
         <v>19</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -2289,7 +2249,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
         <v>70</v>
@@ -2298,7 +2258,7 @@
         <v>19</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -2315,16 +2275,16 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
         <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
@@ -2341,7 +2301,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
         <v>76</v>
@@ -2350,7 +2310,7 @@
         <v>29</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -2367,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
         <v>79</v>
@@ -2376,7 +2336,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -2393,25 +2353,25 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2419,13 +2379,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -2445,25 +2405,25 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2471,7 +2431,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
         <v>93</v>
@@ -2480,7 +2440,7 @@
         <v>19</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
@@ -2497,7 +2457,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
         <v>96</v>
@@ -2506,7 +2466,7 @@
         <v>19</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -2523,7 +2483,7 @@
         <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
         <v>99</v>
@@ -2532,7 +2492,7 @@
         <v>19</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
@@ -2549,16 +2509,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
         <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
@@ -2575,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>105</v>
@@ -2584,7 +2544,7 @@
         <v>29</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
@@ -2601,16 +2561,16 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
         <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
@@ -2627,25 +2587,25 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2653,7 +2613,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -2662,7 +2622,7 @@
         <v>19</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -2679,7 +2639,7 @@
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C35" t="s">
         <v>118</v>
@@ -2688,7 +2648,7 @@
         <v>19</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -2705,7 +2665,7 @@
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
         <v>121</v>
@@ -2714,7 +2674,7 @@
         <v>19</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -2731,16 +2691,16 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
         <v>124</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -2757,7 +2717,7 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
         <v>127</v>
@@ -2766,7 +2726,7 @@
         <v>29</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -2783,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
         <v>130</v>
@@ -2792,7 +2752,7 @@
         <v>29</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
@@ -2809,16 +2769,16 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="E40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
@@ -2835,13 +2795,13 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
         <v>136</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E41">
         <v>8</v>
@@ -2861,25 +2821,25 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="E42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2887,7 +2847,7 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C43" t="s">
         <v>143</v>
@@ -2913,7 +2873,7 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
         <v>146</v>
@@ -2922,7 +2882,7 @@
         <v>29</v>
       </c>
       <c r="E44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -2939,13 +2899,13 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
         <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="E45">
         <v>8</v>
@@ -2965,13 +2925,13 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
         <v>152</v>
       </c>
       <c r="D46" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E46">
         <v>8</v>
@@ -2991,13 +2951,13 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
         <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E47">
         <v>8</v>
@@ -3017,13 +2977,13 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C48" t="s">
         <v>158</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -3040,48 +3000,48 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C49" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="G49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H49" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
+      <c r="F50" t="s">
         <v>164</v>
-      </c>
-      <c r="B50" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" t="s">
-        <v>166</v>
-      </c>
-      <c r="D50" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>167</v>
       </c>
       <c r="G50" t="s">
         <v>168</v>
@@ -3092,22 +3052,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C51" t="s">
         <v>170</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E51">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G51" t="s">
         <v>171</v>
@@ -3118,22 +3078,22 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C52" t="s">
         <v>173</v>
       </c>
       <c r="D52" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E52">
         <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G52" t="s">
         <v>174</v>
@@ -3144,22 +3104,22 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B53" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C53" t="s">
         <v>176</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E53">
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G53" t="s">
         <v>177</v>
@@ -3170,22 +3130,22 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B54" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s">
         <v>179</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E54">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G54" t="s">
         <v>180</v>
@@ -3196,48 +3156,48 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B55" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
         <v>182</v>
       </c>
       <c r="D55" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="E55">
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D56" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E56">
         <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G56" t="s">
         <v>187</v>
@@ -3248,22 +3208,22 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
         <v>189</v>
       </c>
       <c r="D57" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E57">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G57" t="s">
         <v>190</v>
@@ -3274,496 +3234,418 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C58" t="s">
         <v>192</v>
       </c>
       <c r="D58" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E58">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F58" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B59" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C59" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E59">
         <v>11</v>
       </c>
       <c r="F59" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G59" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" t="s">
         <v>197</v>
-      </c>
-      <c r="H59" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B60" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C60" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="D60" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E60">
         <v>11</v>
       </c>
       <c r="F60" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H60" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="C61" t="s">
+        <v>201</v>
+      </c>
+      <c r="D61" t="s">
         <v>202</v>
       </c>
-      <c r="D61" t="s">
-        <v>196</v>
-      </c>
       <c r="E61">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="G61" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B62" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D62" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="C63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D63" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E63">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B64" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C64" t="s">
         <v>212</v>
       </c>
       <c r="D64" t="s">
+        <v>202</v>
+      </c>
+      <c r="E64">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>203</v>
+      </c>
+      <c r="G64" t="s">
         <v>213</v>
       </c>
-      <c r="E64">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="H64" t="s">
         <v>214</v>
-      </c>
-      <c r="G64" t="s">
-        <v>215</v>
-      </c>
-      <c r="H64" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C65" t="s">
+        <v>215</v>
+      </c>
+      <c r="D65" t="s">
+        <v>202</v>
+      </c>
+      <c r="E65">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>203</v>
+      </c>
+      <c r="G65" t="s">
+        <v>216</v>
+      </c>
+      <c r="H65" t="s">
         <v>217</v>
-      </c>
-      <c r="D65" t="s">
-        <v>213</v>
-      </c>
-      <c r="E65">
-        <v>12</v>
-      </c>
-      <c r="F65" t="s">
-        <v>214</v>
-      </c>
-      <c r="G65" t="s">
-        <v>218</v>
-      </c>
-      <c r="H65" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B66" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C66" t="s">
+        <v>218</v>
+      </c>
+      <c r="D66" t="s">
+        <v>202</v>
+      </c>
+      <c r="E66">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>203</v>
+      </c>
+      <c r="G66" t="s">
+        <v>219</v>
+      </c>
+      <c r="H66" t="s">
         <v>220</v>
-      </c>
-      <c r="D66" t="s">
-        <v>213</v>
-      </c>
-      <c r="E66">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>214</v>
-      </c>
-      <c r="G66" t="s">
-        <v>221</v>
-      </c>
-      <c r="H66" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B67" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
+        <v>221</v>
+      </c>
+      <c r="D67" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>203</v>
+      </c>
+      <c r="G67" t="s">
+        <v>222</v>
+      </c>
+      <c r="H67" t="s">
         <v>223</v>
-      </c>
-      <c r="D67" t="s">
-        <v>213</v>
-      </c>
-      <c r="E67">
-        <v>12</v>
-      </c>
-      <c r="F67" t="s">
-        <v>214</v>
-      </c>
-      <c r="G67" t="s">
-        <v>224</v>
-      </c>
-      <c r="H67" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C68" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" t="s">
+        <v>225</v>
+      </c>
+      <c r="E68">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>203</v>
+      </c>
+      <c r="G68" t="s">
         <v>226</v>
       </c>
-      <c r="D68" t="s">
-        <v>213</v>
-      </c>
-      <c r="E68">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
-        <v>214</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>227</v>
-      </c>
-      <c r="H68" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B69" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C69" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D69" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E69">
         <v>13</v>
       </c>
       <c r="F69" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G69" t="s">
+        <v>229</v>
+      </c>
+      <c r="H69" t="s">
         <v>230</v>
-      </c>
-      <c r="H69" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B70" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C70" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D70" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E70">
         <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G70" t="s">
+        <v>232</v>
+      </c>
+      <c r="H70" t="s">
         <v>233</v>
-      </c>
-      <c r="H70" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B71" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C71" t="s">
+        <v>234</v>
+      </c>
+      <c r="D71" t="s">
+        <v>225</v>
+      </c>
+      <c r="E71">
+        <v>14</v>
+      </c>
+      <c r="F71" t="s">
+        <v>203</v>
+      </c>
+      <c r="G71" t="s">
         <v>235</v>
       </c>
-      <c r="D71" t="s">
+      <c r="H71" t="s">
         <v>236</v>
-      </c>
-      <c r="E71">
-        <v>13</v>
-      </c>
-      <c r="F71" t="s">
-        <v>214</v>
-      </c>
-      <c r="G71" t="s">
-        <v>237</v>
-      </c>
-      <c r="H71" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B72" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C72" t="s">
+        <v>237</v>
+      </c>
+      <c r="D72" t="s">
+        <v>225</v>
+      </c>
+      <c r="E72">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>203</v>
+      </c>
+      <c r="G72" t="s">
+        <v>238</v>
+      </c>
+      <c r="H72" t="s">
         <v>239</v>
-      </c>
-      <c r="D72" t="s">
-        <v>236</v>
-      </c>
-      <c r="E72">
-        <v>13</v>
-      </c>
-      <c r="F72" t="s">
-        <v>214</v>
-      </c>
-      <c r="G72" t="s">
-        <v>240</v>
-      </c>
-      <c r="H72" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
+        <v>240</v>
+      </c>
+      <c r="D73" t="s">
+        <v>225</v>
+      </c>
+      <c r="E73">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>203</v>
+      </c>
+      <c r="G73" t="s">
+        <v>241</v>
+      </c>
+      <c r="H73" t="s">
         <v>242</v>
-      </c>
-      <c r="D73" t="s">
-        <v>236</v>
-      </c>
-      <c r="E73">
-        <v>13</v>
-      </c>
-      <c r="F73" t="s">
-        <v>214</v>
-      </c>
-      <c r="G73" t="s">
-        <v>243</v>
-      </c>
-      <c r="H73" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" t="s">
-        <v>164</v>
-      </c>
-      <c r="B74" t="s">
-        <v>211</v>
-      </c>
-      <c r="C74" t="s">
-        <v>245</v>
-      </c>
-      <c r="D74" t="s">
-        <v>236</v>
-      </c>
-      <c r="E74">
-        <v>14</v>
-      </c>
-      <c r="F74" t="s">
-        <v>214</v>
-      </c>
-      <c r="G74" t="s">
-        <v>246</v>
-      </c>
-      <c r="H74" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" t="s">
-        <v>164</v>
-      </c>
-      <c r="B75" t="s">
-        <v>211</v>
-      </c>
-      <c r="C75" t="s">
-        <v>248</v>
-      </c>
-      <c r="D75" t="s">
-        <v>236</v>
-      </c>
-      <c r="E75">
-        <v>14</v>
-      </c>
-      <c r="F75" t="s">
-        <v>214</v>
-      </c>
-      <c r="G75" t="s">
-        <v>249</v>
-      </c>
-      <c r="H75" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="A76" t="s">
-        <v>164</v>
-      </c>
-      <c r="B76" t="s">
-        <v>211</v>
-      </c>
-      <c r="C76" t="s">
-        <v>251</v>
-      </c>
-      <c r="D76" t="s">
-        <v>236</v>
-      </c>
-      <c r="E76">
-        <v>14</v>
-      </c>
-      <c r="F76" t="s">
-        <v>214</v>
-      </c>
-      <c r="G76" t="s">
-        <v>252</v>
-      </c>
-      <c r="H76" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
